--- a/2_Formulas_Functions/2_Functions_Intro.xlsx
+++ b/2_Formulas_Functions/2_Functions_Intro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Mac\Home\Developer\_Courses\Excel\Excel_Data_Analytics_Course\2_Formulas_Functions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f943803864469b1e/Documents/GitHub/Excel_Data_Analytics/Excel_project_data_analysis/2_Formulas_Functions/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF50AE8-6F59-4DF5-B44C-2445C4C088D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-42890" yWindow="-19270" windowWidth="18350" windowHeight="10350" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="9" r:id="rId1"/>
@@ -999,32 +999,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8DE2224-2E95-4FCC-A032-AA541E0AE3D4}">
   <dimension ref="B1:S17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.15625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.68359375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.41796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.26171875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.578125" style="1" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" style="1" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1" hidden="1" customWidth="1"/>
     <col min="8" max="9" width="11" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="14.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.15625" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="14.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" style="1" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="10.41796875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.15625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.83984375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.88671875" style="1" customWidth="1"/>
     <col min="17" max="17" width="9" style="1"/>
     <col min="18" max="18" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G1" s="28"/>
     </row>
-    <row r="2" spans="2:19" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:19" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="5" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="P5" s="22"/>
     </row>
-    <row r="6" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="P6" s="22"/>
     </row>
-    <row r="7" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="P7" s="22"/>
     </row>
-    <row r="8" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="P8" s="22"/>
     </row>
-    <row r="9" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P9" s="22"/>
     </row>
-    <row r="10" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="P10" s="22"/>
     </row>
-    <row r="11" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="22"/>
     </row>
-    <row r="12" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="15" t="s">
         <v>9</v>
       </c>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="P12" s="22"/>
     </row>
-    <row r="13" spans="2:19" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:19" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B13" s="29" t="s">
         <v>27</v>
       </c>
@@ -1645,7 +1645,7 @@
       <c r="D13" s="19"/>
       <c r="E13" s="30"/>
     </row>
-    <row r="14" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="31" t="s">
         <v>28</v>
       </c>
@@ -1653,7 +1653,7 @@
       <c r="D14" s="20"/>
       <c r="E14" s="32"/>
     </row>
-    <row r="15" spans="2:19" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:19" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B15" s="29" t="s">
         <v>30</v>
       </c>
@@ -1661,7 +1661,7 @@
       <c r="D15" s="19"/>
       <c r="E15" s="30"/>
     </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B16" s="33" t="s">
         <v>31</v>
       </c>
@@ -1669,7 +1669,7 @@
       <c r="D16" s="18"/>
       <c r="E16" s="34"/>
     </row>
-    <row r="17" spans="2:5" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="12" t="s">
         <v>31</v>
       </c>
@@ -1685,32 +1685,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D423364-12D3-4C3A-8A6B-C3645EBFE927}">
   <dimension ref="B1:S17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.15625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.68359375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.41796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.26171875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.578125" style="1" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" style="1" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1" hidden="1" customWidth="1"/>
     <col min="8" max="9" width="11" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="14.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.15625" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="14.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" style="1" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="10.41796875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.15625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.83984375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.88671875" style="1" customWidth="1"/>
     <col min="17" max="17" width="9" style="1"/>
     <col min="18" max="18" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G1" s="28"/>
     </row>
-    <row r="2" spans="2:19" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:19" s="8" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="5" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="15" t="s">
         <v>9</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:19" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:19" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B13" s="29" t="s">
         <v>27</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>10400</v>
       </c>
     </row>
-    <row r="14" spans="2:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="31" t="s">
         <v>28</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="15" spans="2:19" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:19" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B15" s="29" t="s">
         <v>30</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B16" s="33" t="s">
         <v>31</v>
       </c>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="E16" s="34"/>
     </row>
-    <row r="17" spans="2:5" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="12" t="s">
         <v>31</v>
       </c>
@@ -2444,15 +2444,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08EBE098-CD97-45AE-AE7E-86DF2D94E426}">
   <dimension ref="B2:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.1015625" customWidth="1"/>
-    <col min="2" max="2" width="13.41796875" customWidth="1"/>
-    <col min="3" max="3" width="31.41796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="60.41796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.109375" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="3" width="31.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="60.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B2" s="37" t="s">
         <v>32</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="38" t="e">
         <f>1/0</f>
         <v>#DIV/0!</v>
@@ -2475,7 +2475,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="38" t="e">
         <f>A4 + "text"</f>
         <v>#VALUE!</v>
@@ -2487,7 +2487,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="9" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -2499,7 +2499,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="e" cm="1">
         <f t="array" aca="1" ref="B6" ca="1">COUNTT(A3:A9)</f>
         <v>#NAME?</v>
@@ -2511,7 +2511,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="38" t="e">
         <f>VLOOKUP("Value", A1:A10, 2, FALSE)</f>
         <v>#N/A</v>
@@ -2523,7 +2523,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" s="38" t="e">
         <f>SQRT(-1)</f>
         <v>#NUM!</v>
@@ -2535,7 +2535,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="38" t="e">
         <f>SUM(A1:A10 C1:C10)</f>
         <v>#NULL!</v>
